--- a/outputs/evaluation/requirement/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/CF_M01_req_eval.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9167</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9167</v>
+        <v>0.88</v>
       </c>
       <c r="C15" t="n">
         <v>0.7333</v>
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2108,61 +2108,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>R_18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_R20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The system must be available at all times, except for some punctuality, such as an update.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8447</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M01_R21</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>The system must be able to support an unlimited number of
 connections at the same time.</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>0.8163</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>The system scales automatically as data increases.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CF_M01_R22</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>The system must be able to grow in capacity as the volume of data increases.</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>0.8692</v>
       </c>
     </row>
